--- a/data/gst/schema/public/get-day-wise-changed-gstins/v1.0/fields.xlsx
+++ b/data/gst/schema/public/get-day-wise-changed-gstins/v1.0/fields.xlsx
@@ -805,7 +805,7 @@
         <v>29</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" x14ac:dyDescent="0.25">
